--- a/data/compare/PENDING_SYNC_CATEGORIES_C_to_H.xlsx
+++ b/data/compare/PENDING_SYNC_CATEGORIES_C_to_H.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId2"/>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">C_Hold_Exact_Lock!$A$1:$G$68</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">D_Hold_Partial_Conflict!$A$1:$G$29</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">E_Sheet_Only_NonHold!$A$1:$G$72</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">E_Sheet_Only_NonHold!$A$1:$G$64</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">F_Sheet_Only_Hold!$A$1:$G$21</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">G_DB_Only_NonHold!$A$1:$G$23</definedName>
     <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">H_DB_Only_Hold!$A$1:$G$4</definedName>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="374">
   <si>
     <t xml:space="preserve">Sarveda pending sync — PRODUCTS ONLY (courses/events excluded)</t>
   </si>
@@ -768,258 +768,246 @@
     <t xml:space="preserve">HCB-C-N</t>
   </si>
   <si>
+    <t xml:space="preserve">25 Rods -Bar Chime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-BCH-25</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sheet-only product</t>
   </si>
   <si>
-    <t xml:space="preserve">25 Rods -Bar Chime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-BCH-25</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bamboo Rainstick with Bag</t>
   </si>
   <si>
     <t xml:space="preserve">MI-BR-WB</t>
   </si>
   <si>
-    <t xml:space="preserve">Bottle</t>
+    <t xml:space="preserve">Clay Whistle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-CW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crystal Bowls - Coloured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-CB-C-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-CB-C-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-CB-C-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-CB-C-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-CB-C-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-CB-C-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-CB-C-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-CB-C-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-CB-C-9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Etched Chau Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-ECG-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-ECG-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-ECG-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-ECG-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-ECG-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28INCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-ECG-28-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32 in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-ECG-32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32INCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-ECG-32-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36 in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-ECG-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40INCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-ECG-40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Happiness is Inside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">with-brush / 1L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HII-B-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native American Flute - Double</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Double</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-NAF-D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native American Flute - Single Large</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single Large</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-NAF-SL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native American Flute - Single Medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single Medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-NAF-SM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native American Flute - Single Small</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single Small</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-NAF-SS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native American Flute - Triple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Triple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-NAF-T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ocarina - Big</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Big</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-OC-B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ocarina - Small</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-OC-S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overtone Flute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-OF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pink &amp; Positive</t>
   </si>
   <si>
     <t xml:space="preserve">with-brush / 500ml</t>
   </si>
   <si>
-    <t xml:space="preserve">BO-B-.5</t>
+    <t xml:space="preserve">PP-B-.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PP-B-1</t>
   </si>
   <si>
     <t xml:space="preserve">without-brush / 500ml</t>
   </si>
   <si>
-    <t xml:space="preserve">BO-N-.5</t>
+    <t xml:space="preserve">PP-N-.5</t>
   </si>
   <si>
     <t xml:space="preserve">without-brush / 1L</t>
   </si>
   <si>
-    <t xml:space="preserve">BO-N-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clay Whistle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-CW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crystal Bowls - Coloured</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-CB-C-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-CB-C-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-CB-C-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-CB-C-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-CB-C-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-CB-C-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-CB-C-7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-CB-C-8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-CB-C-9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Etched Chau Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-ECG-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-ECG-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-ECG-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-ECG-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-ECG-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28INCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-ECG-28-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32 in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-ECG-32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32INCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-ECG-32-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36 in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-ECG-36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40INCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-ECG-40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Happiness is Inside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">with-brush / 1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HII-B-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Native American Flute - Double</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Double</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-NAF-D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Native American Flute - Single Large</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single Large</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-NAF-SL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Native American Flute - Single Medium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single Medium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-NAF-SM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Native American Flute - Single Small</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single Small</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-NAF-SS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Native American Flute - Triple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Triple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-NAF-T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ocarina - Big</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Big</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-OC-B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ocarina - Small</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Small</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-OC-S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overtone Flute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-OF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pink &amp; Positive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PP-B-.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PP-B-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PP-N-.5</t>
-  </si>
-  <si>
     <t xml:space="preserve">PP-N-1</t>
   </si>
   <si>
@@ -1122,33 +1110,15 @@
     <t xml:space="preserve">MI-WC-YE-S</t>
   </si>
   <si>
-    <t xml:space="preserve">32 Rods - Bar Chime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-BCH-32</t>
+    <t xml:space="preserve">8 Keys Wooden Xylophone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI-XP-W-8</t>
   </si>
   <si>
     <t xml:space="preserve">DB-only product</t>
   </si>
   <si>
-    <t xml:space="preserve">8 Keys Wooden Xylophone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-XP-W-8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aluminium 22 Steel Bars Chime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-Ch-BS-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bamboo Jaw Harp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-BJH</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kenari Seed Shell Shakers</t>
   </si>
   <si>
@@ -1159,63 +1129,6 @@
   </si>
   <si>
     <t xml:space="preserve">MI-KS-S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mini Bamboo Slide Whistle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-B-SW-D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-B-SW-S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single Painted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-B-SW-S-P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mini Tongue Drum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-TD-6.3-B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-TD-6.3-G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-TD-6.3-P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-TD-6.3-Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Native American Style Flute – Handcrafted Wooden Melody Maker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-NM-F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natural Bamboo Xylophone with 5 Keys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI-XP-B-5</t>
   </si>
   <si>
     <t xml:space="preserve">Rectangular Yoga Bolster</t>
@@ -1298,7 +1211,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1315,6 +1228,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F2A1"/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1367,7 +1286,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1400,6 +1319,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1409,7 +1336,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1443,6 +1370,13 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE8F2A1"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1484,7 +1418,7 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFE8F2A1"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -4150,7 +4084,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G1048576"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="55"/>
@@ -4186,26 +4120,38 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7"/>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
+        <v>244</v>
+      </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+      <c r="C2" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>174</v>
+      </c>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
       <c r="G2" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="3" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4215,9 +4161,7 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
-      <c r="G4" s="7" t="s">
-        <v>244</v>
-      </c>
+      <c r="G4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7"/>
@@ -4226,9 +4170,7 @@
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="7" t="s">
-        <v>244</v>
-      </c>
+      <c r="G5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7"/>
@@ -4237,369 +4179,395 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7"/>
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>249</v>
+      </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
+      <c r="C7" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>174</v>
+      </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="C12" s="7" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="8" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="B13" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="B14" s="7" t="s">
+      <c r="D8" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="9" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+      <c r="D9" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="10" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
+      <c r="D10" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="11" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="D11" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="12" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="B17" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="D12" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="13" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="B18" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="D13" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="14" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="D18" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="B19" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D14" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="15" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="B20" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="D15" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="16" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="B21" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="D16" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="17" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="B22" s="7" t="s">
+      <c r="B17" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="D22" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="B23" s="7" t="s">
+      <c r="D17" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="18" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="B24" s="7" t="s">
+      <c r="D18" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="19" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="D24" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
+      <c r="D19" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="20" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="C20" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="D20" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="21" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="B26" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="D21" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="22" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7" t="s">
-        <v>244</v>
+      <c r="C22" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="23" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="24" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="25" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="26" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>174</v>
@@ -4607,18 +4575,18 @@
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
       <c r="G27" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>174</v>
@@ -4626,18 +4594,18 @@
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
       <c r="G28" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>174</v>
@@ -4645,18 +4613,18 @@
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
       <c r="G29" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>174</v>
@@ -4664,18 +4632,18 @@
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>277</v>
+        <v>303</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>174</v>
@@ -4683,18 +4651,18 @@
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>277</v>
+        <v>306</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>174</v>
@@ -4702,18 +4670,18 @@
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>174</v>
@@ -4721,18 +4689,18 @@
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>277</v>
+        <v>312</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>174</v>
@@ -4740,18 +4708,16 @@
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
       <c r="G34" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>299</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="B35" s="7"/>
       <c r="C35" s="7" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>174</v>
@@ -4759,18 +4725,18 @@
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>174</v>
@@ -4778,18 +4744,18 @@
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>174</v>
@@ -4797,18 +4763,18 @@
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>174</v>
@@ -4816,18 +4782,18 @@
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>174</v>
@@ -4835,18 +4801,16 @@
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>314</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="B40" s="7"/>
       <c r="C40" s="7" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>174</v>
@@ -4854,18 +4818,18 @@
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>174</v>
@@ -4873,18 +4837,18 @@
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>320</v>
+        <v>292</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>174</v>
@@ -4892,16 +4856,18 @@
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="B43" s="7"/>
+        <v>327</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>321</v>
+      </c>
       <c r="C43" s="7" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>174</v>
@@ -4909,18 +4875,18 @@
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>250</v>
+        <v>323</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>174</v>
@@ -4928,18 +4894,18 @@
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>299</v>
+        <v>333</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>174</v>
@@ -4947,18 +4913,18 @@
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>252</v>
+        <v>335</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>174</v>
@@ -4966,18 +4932,18 @@
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>254</v>
+        <v>338</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>174</v>
@@ -4985,16 +4951,18 @@
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="B48" s="7"/>
+        <v>337</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>340</v>
+      </c>
       <c r="C48" s="7" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>174</v>
@@ -5002,18 +4970,18 @@
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>250</v>
+        <v>342</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>174</v>
@@ -5021,18 +4989,18 @@
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
       <c r="G49" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>299</v>
+        <v>344</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>174</v>
@@ -5040,18 +5008,18 @@
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
       <c r="G50" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>252</v>
+        <v>346</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>174</v>
@@ -5059,18 +5027,18 @@
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>254</v>
+        <v>348</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>174</v>
@@ -5078,18 +5046,18 @@
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>174</v>
@@ -5097,18 +5065,18 @@
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>174</v>
@@ -5116,18 +5084,18 @@
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
       <c r="G54" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>174</v>
@@ -5135,18 +5103,18 @@
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
       <c r="G55" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>174</v>
@@ -5154,251 +5122,107 @@
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
       <c r="G56" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>174</v>
-      </c>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="7"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
       <c r="G57" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>174</v>
-      </c>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="7"/>
+      <c r="B58" s="7"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
       <c r="E58" s="7"/>
       <c r="F58" s="7"/>
       <c r="G58" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>174</v>
-      </c>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="7"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
       <c r="E59" s="7"/>
       <c r="F59" s="7"/>
       <c r="G59" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>174</v>
-      </c>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="7"/>
+      <c r="B60" s="7"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
       <c r="G60" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>174</v>
-      </c>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="7"/>
+      <c r="B61" s="7"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
       <c r="E61" s="7"/>
       <c r="F61" s="7"/>
       <c r="G61" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>174</v>
-      </c>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="7"/>
+      <c r="B62" s="7"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
       <c r="E62" s="7"/>
       <c r="F62" s="7"/>
       <c r="G62" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>174</v>
-      </c>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="7"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
       <c r="E63" s="7"/>
       <c r="F63" s="7"/>
       <c r="G63" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>174</v>
-      </c>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="7"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
       <c r="E64" s="7"/>
       <c r="F64" s="7"/>
       <c r="G64" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
-      <c r="G65" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7"/>
-      <c r="B66" s="7"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
-      <c r="G66" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="7"/>
-      <c r="B67" s="7"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
-      <c r="G67" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="7"/>
-      <c r="B68" s="7"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="7"/>
-      <c r="B69" s="7"/>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="7"/>
-      <c r="G69" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="7"/>
-      <c r="B70" s="7"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="7"/>
-      <c r="B71" s="7"/>
-      <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="7"/>
-      <c r="G71" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="7"/>
-      <c r="B72" s="7"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-      <c r="G72" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A1:G72"/>
+  <autoFilter ref="A1:G64"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5418,7 +5242,7 @@
   <dimension ref="A1:G1048576"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="69.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="10"/>
@@ -5452,29 +5276,21 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>362</v>
-      </c>
+      <c r="A2" s="7"/>
       <c r="B2" s="7"/>
-      <c r="C2" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>180</v>
-      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
-        <v>364</v>
-      </c>
+      <c r="G2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>180</v>
@@ -5482,52 +5298,36 @@
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
       <c r="G3" s="7" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>367</v>
-      </c>
+      <c r="A4" s="7"/>
       <c r="B4" s="7"/>
-      <c r="C4" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>180</v>
-      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
-      <c r="G4" s="7" t="s">
-        <v>364</v>
-      </c>
+      <c r="G4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>369</v>
-      </c>
+      <c r="A5" s="7"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>180</v>
-      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="7" t="s">
-        <v>364</v>
-      </c>
+      <c r="G5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>180</v>
@@ -5535,18 +5335,18 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>180</v>
@@ -5554,185 +5354,99 @@
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>180</v>
-      </c>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
-      <c r="G8" s="7" t="s">
-        <v>364</v>
-      </c>
+      <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>180</v>
-      </c>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
-      <c r="G9" s="7" t="s">
-        <v>364</v>
-      </c>
+      <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>180</v>
-      </c>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="7" t="s">
-        <v>364</v>
-      </c>
+      <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>180</v>
-      </c>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
-      <c r="G11" s="7" t="s">
-        <v>364</v>
-      </c>
+      <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>180</v>
-      </c>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
-      <c r="G12" s="7" t="s">
-        <v>364</v>
-      </c>
+      <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>180</v>
-      </c>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
-      <c r="G13" s="7" t="s">
-        <v>364</v>
-      </c>
+      <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>180</v>
-      </c>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
-      <c r="G14" s="7" t="s">
-        <v>364</v>
-      </c>
+      <c r="G14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>390</v>
-      </c>
+      <c r="A15" s="7"/>
       <c r="B15" s="7"/>
-      <c r="C15" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>180</v>
-      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
-      <c r="G15" s="7" t="s">
-        <v>364</v>
-      </c>
+      <c r="G15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>392</v>
-      </c>
+      <c r="A16" s="7"/>
       <c r="B16" s="7"/>
-      <c r="C16" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>180</v>
-      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="7" t="s">
-        <v>364</v>
-      </c>
+      <c r="G16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>394</v>
+        <v>365</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>103</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>395</v>
+        <v>366</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>180</v>
@@ -5740,18 +5454,18 @@
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>394</v>
+        <v>365</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>122</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>396</v>
+        <v>367</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>180</v>
@@ -5759,18 +5473,18 @@
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>394</v>
+        <v>365</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>138</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>397</v>
+        <v>368</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>180</v>
@@ -5778,18 +5492,18 @@
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>394</v>
+        <v>365</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>109</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>398</v>
+        <v>369</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>180</v>
@@ -5797,18 +5511,18 @@
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>394</v>
+        <v>365</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>399</v>
+        <v>370</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>400</v>
+        <v>371</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>180</v>
@@ -5816,18 +5530,18 @@
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>394</v>
+        <v>365</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>111</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>401</v>
+        <v>372</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>180</v>
@@ -5835,7 +5549,7 @@
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5933,7 +5647,7 @@
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
       <c r="G2" s="7" t="s">
-        <v>402</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5952,7 +5666,7 @@
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
       <c r="G3" s="7" t="s">
-        <v>402</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5971,7 +5685,7 @@
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7" t="s">
-        <v>402</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
